--- a/AI工作区/配置表/ItemEffectTable.xlsx
+++ b/AI工作区/配置表/ItemEffectTable.xlsx
@@ -1444,7 +1444,7 @@
         <v>36</v>
       </c>
       <c r="S4" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:19">
